--- a/du_lieu_nhap_kho_y_te.xlsx
+++ b/du_lieu_nhap_kho_y_te.xlsx
@@ -398,22 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N14"/>
-  <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
-    <col min="11" max="11" width="22.83203125" customWidth="1"/>
-    <col min="12" max="12" width="22.83203125" customWidth="1"/>
-    <col min="13" max="13" width="22.83203125" customWidth="1"/>
-    <col min="14" max="14" width="22.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -535,7 +519,7 @@
         <v>PM-2023-B</v>
       </c>
       <c r="K3" t="str">
-        <v>NCC-002</v>
+        <v>NCC-001</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -623,7 +607,7 @@
         <v>AED-500</v>
       </c>
       <c r="K5" t="str">
-        <v>NCC-002</v>
+        <v>NCC-001</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -711,7 +695,7 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>NCC-002</v>
+        <v>NCC-001</v>
       </c>
       <c r="L7">
         <v>20</v>
@@ -799,7 +783,7 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>NCC-002</v>
+        <v>NCC-001</v>
       </c>
       <c r="L9">
         <v>50</v>
@@ -887,7 +871,7 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>NCC-002</v>
+        <v>NCC-001</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -975,7 +959,7 @@
         <v>SCL-55</v>
       </c>
       <c r="K13" t="str">
-        <v>NCC-002</v>
+        <v>NCC-001</v>
       </c>
       <c r="L13">
         <v>5</v>
